--- a/data/gravel/Cervelo Aspero 5 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 5 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9AA5CE7-5A34-A549-95B3-FA8BCF6C72E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB34366-338F-2848-BD57-5E3EBF0EA819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34240" yWindow="-20360" windowWidth="26840" windowHeight="15460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4160" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
   <si>
     <t>brand</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>a8:h33</t>
+  </si>
+  <si>
+    <t>https://www.cervelo.com/_next/image?url=https%3A%2F%2Fimages.prismic.io%2Fcervelo%2FaDiwqydWJ-7kSs6F_0L0ALBFE2C-PROFILE-Web.png%3Fauto%3Dformat%2Ccompress&amp;w=2600&amp;q=99</t>
   </si>
 </sst>
 </file>
@@ -709,6 +712,11 @@
         <v>93</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>97</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Cervelo Aspero 5 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 5 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB34366-338F-2848-BD57-5E3EBF0EA819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDC2482-9B26-E740-B0E4-2150B419D3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4160" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="100">
   <si>
     <t>brand</t>
   </si>
@@ -317,9 +317,6 @@
     <t>https://www.cervelo.com/en-US/bikes/aspero-5</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Aspero 5</t>
   </si>
   <si>
@@ -327,6 +324,15 @@
   </si>
   <si>
     <t>https://www.cervelo.com/_next/image?url=https%3A%2F%2Fimages.prismic.io%2Fcervelo%2FaDiwqydWJ-7kSs6F_0L0ALBFE2C-PROFILE-Web.png%3Fauto%3Dformat%2Ccompress&amp;w=2600&amp;q=99</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Aliso Viejo, California, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -666,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -685,7 +691,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -714,7 +720,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -722,7 +728,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1516,7 +1522,15 @@
         <v>84</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>94</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>97</v>
+      </c>
+      <c r="B74" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Cervelo Aspero 5 2025.xlsx
+++ b/data/gravel/Cervelo Aspero 5 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBDC2482-9B26-E740-B0E4-2150B419D3ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F513D361-B5FA-F341-A08D-70A1CABFFE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -333,6 +333,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -672,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1383,153 +1401,183 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>60</v>
-      </c>
-      <c r="B50" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>64</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>65</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>60</v>
+      </c>
+      <c r="B56" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>73</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>74</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>76</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>79</v>
+        <v>73</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>80</v>
+        <v>74</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>81</v>
-      </c>
-      <c r="B70">
-        <v>5500</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>82</v>
-      </c>
-      <c r="B71">
-        <v>8700</v>
+        <v>76</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>84</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77">
+        <v>8700</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>97</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>98</v>
       </c>
     </row>
